--- a/placental_development/spongiotrophoblast_layer_developmental_growth_GO0090214.xlsx
+++ b/placental_development/spongiotrophoblast_layer_developmental_growth_GO0090214.xlsx
@@ -1,21 +1,92 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b2cd7fd51b7c34e8/Desktop/ongoing/Rproj/SofiaAnalise/placental_development/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_AC7DFDCE8F79A8D366075C52F322FAF3CD178B1A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0547E789-0C98-4C17-9705-7C28C65C2CE4}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>GeneRatio</t>
+  </si>
+  <si>
+    <t>BgRatio</t>
+  </si>
+  <si>
+    <t>RichFactor</t>
+  </si>
+  <si>
+    <t>FoldEnrichment</t>
+  </si>
+  <si>
+    <t>zScore</t>
+  </si>
+  <si>
+    <t>pvalue</t>
+  </si>
+  <si>
+    <t>p.adjust</t>
+  </si>
+  <si>
+    <t>qvalue</t>
+  </si>
+  <si>
+    <t>geneID</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>allergic asthma</t>
+  </si>
+  <si>
+    <t>1/1</t>
+  </si>
+  <si>
+    <t>363/17907</t>
+  </si>
+  <si>
+    <t>PLAC1</t>
+  </si>
+  <si>
+    <t>burkitt lymphoma</t>
+  </si>
+  <si>
+    <t>397/17907</t>
+  </si>
+  <si>
+    <t>hydrocephalus</t>
+  </si>
+  <si>
+    <t>446/17907</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +134,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +186,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +220,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +255,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,202 +431,153 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.08984375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>GeneRatio</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>BgRatio</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>RichFactor</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>FoldEnrichment</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>zScore</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>pvalue</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>p.adjust</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>qvalue</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>geneID</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
+    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>allergic asthma</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>allergic asthma</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>363/17907</t>
-        </is>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>0.002754820936639119</v>
+        <v>2.7548209366391198E-3</v>
       </c>
       <c r="F2">
-        <v>49.3305785123967</v>
+        <v>49.330578512396698</v>
       </c>
       <c r="G2">
         <v>6.952019743383695</v>
       </c>
       <c r="H2">
-        <v>0.02027140224493229</v>
+        <v>2.0271402244932291E-2</v>
       </c>
       <c r="I2">
-        <v>0.02490646116044015</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>PLAC1</t>
-        </is>
+        <v>2.4906461160440149E-2</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
       </c>
       <c r="L2">
         <v>1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>burkitt lymphoma</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>burkitt lymphoma</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>397/17907</t>
-        </is>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>0.002518891687657431</v>
+        <v>2.5188916876574311E-3</v>
       </c>
       <c r="F3">
-        <v>45.10579345088161</v>
+        <v>45.105793450881613</v>
       </c>
       <c r="G3">
-        <v>6.64121927441653</v>
+        <v>6.6412192744165299</v>
       </c>
       <c r="H3">
-        <v>0.02217010107779072</v>
+        <v>2.2170101077790719E-2</v>
       </c>
       <c r="I3">
-        <v>0.02490646116044015</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>PLAC1</t>
-        </is>
+        <v>2.4906461160440149E-2</v>
+      </c>
+      <c r="K3" t="s">
+        <v>15</v>
       </c>
       <c r="L3">
         <v>1</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>hydrocephalus</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>hydrocephalus</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1/1</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>446/17907</t>
-        </is>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
       </c>
       <c r="E4">
-        <v>0.002242152466367713</v>
+        <v>2.242152466367713E-3</v>
       </c>
       <c r="F4">
-        <v>40.15022421524664</v>
+        <v>40.150224215246638</v>
       </c>
       <c r="G4">
         <v>6.257014001522343</v>
       </c>
       <c r="H4">
-        <v>0.02490646116044015</v>
+        <v>2.4906461160440149E-2</v>
       </c>
       <c r="I4">
-        <v>0.02490646116044015</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>PLAC1</t>
-        </is>
+        <v>2.4906461160440149E-2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>15</v>
       </c>
       <c r="L4">
         <v>1</v>
